--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.12661997255327</v>
+        <v>5.708075745539907</v>
       </c>
       <c r="D2" t="n">
-        <v>29.60075550425485</v>
+        <v>4.810122769441413</v>
       </c>
       <c r="E2" t="n">
-        <v>8.61810196382018</v>
+        <v>1.400441569120779</v>
       </c>
       <c r="F2" t="n">
-        <v>9.882084978631617</v>
+        <v>1.605838809027638</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.66759445415342</v>
+        <v>3.683484098799931</v>
       </c>
       <c r="D3" t="n">
-        <v>26.68532206802087</v>
+        <v>4.336364836053392</v>
       </c>
       <c r="E3" t="n">
-        <v>8.61810196382018</v>
+        <v>1.400441569120779</v>
       </c>
       <c r="F3" t="n">
-        <v>9.882084978631617</v>
+        <v>1.605838809027638</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.13898812881206</v>
+        <v>2.297585570931961</v>
       </c>
       <c r="D4" t="n">
-        <v>48.95350254289258</v>
+        <v>7.954944163220045</v>
       </c>
       <c r="E4" t="n">
-        <v>8.61810196382018</v>
+        <v>1.400441569120779</v>
       </c>
       <c r="F4" t="n">
-        <v>9.882084978631617</v>
+        <v>1.605838809027638</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
